--- a/astro-site/public/dl/kit-plan-financiero/05-pyl-mensual-real-vs-presupuesto.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/05-pyl-mensual-real-vs-presupuesto.xlsx
@@ -1,28 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ene" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Feb" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mar" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Abr" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="May" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Jun" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Jul" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Ago" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Sep" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Oct" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Nov" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Dic" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Resumen Anual" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ene" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feb" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mar" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abr" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="May" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jun" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jul" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ago" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sep" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oct" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nov" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dic" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen Anual" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Ene'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Feb'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mar'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Abr'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'May'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Jun'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Jul'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Ago'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'Sep'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'Oct'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'Nov'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Dic'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Resumen Anual'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -30,8 +44,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.0%" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -152,51 +166,51 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="10" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="11" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -556,15 +570,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B10"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="85"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -572,6 +587,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -579,6 +595,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -614,8 +631,25 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -624,17 +658,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -651,6 +685,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -704,15 +739,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -729,15 +764,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -754,15 +789,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -779,15 +814,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -798,25 +833,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -838,15 +874,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -863,15 +899,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -888,15 +924,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -913,15 +949,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -938,15 +974,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -963,15 +999,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -982,25 +1018,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -1009,23 +1046,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -1036,13 +1073,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -1058,11 +1096,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -1073,11 +1111,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -1088,13 +1126,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -1108,7 +1147,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1117,17 +1165,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1144,6 +1192,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1197,15 +1246,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -1222,15 +1271,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -1247,15 +1296,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -1272,15 +1321,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -1291,25 +1340,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -1331,15 +1381,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -1356,15 +1406,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -1381,15 +1431,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -1406,15 +1456,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -1431,15 +1481,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -1456,15 +1506,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -1475,25 +1525,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -1502,23 +1553,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -1529,13 +1580,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -1551,11 +1603,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -1566,11 +1618,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -1581,13 +1633,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -1601,7 +1654,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1610,17 +1672,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1637,6 +1699,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1690,15 +1753,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -1715,15 +1778,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -1740,15 +1803,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -1765,15 +1828,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -1784,25 +1847,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -1824,15 +1888,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -1849,15 +1913,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -1874,15 +1938,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -1899,15 +1963,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -1924,15 +1988,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -1949,15 +2013,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -1968,25 +2032,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -1995,23 +2060,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -2022,13 +2087,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -2044,11 +2110,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -2059,11 +2125,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -2074,13 +2140,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -2094,7 +2161,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2103,17 +2179,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2130,6 +2206,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2183,15 +2260,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -2208,15 +2285,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -2233,15 +2310,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -2258,15 +2335,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -2277,25 +2354,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -2317,15 +2395,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -2342,15 +2420,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -2367,15 +2445,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -2392,15 +2470,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -2417,15 +2495,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -2442,15 +2520,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -2461,25 +2539,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -2488,23 +2567,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -2515,13 +2594,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -2537,11 +2617,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -2552,11 +2632,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -2567,13 +2647,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -2587,7 +2668,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2596,25 +2686,25 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="14"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="14"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
-    <col customWidth="1" max="7" min="7" width="14"/>
-    <col customWidth="1" max="8" min="8" width="14"/>
-    <col customWidth="1" max="9" min="9" width="14"/>
-    <col customWidth="1" max="10" min="10" width="14"/>
-    <col customWidth="1" max="11" min="11" width="14"/>
-    <col customWidth="1" max="12" min="12" width="14"/>
-    <col customWidth="1" max="13" min="13" width="14"/>
-    <col customWidth="1" max="14" min="14" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2631,6 +2721,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2979,6 +3070,9 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
@@ -2992,7 +3086,16 @@
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A14:N14"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3001,17 +3104,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3028,6 +3131,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -3081,15 +3185,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -3106,15 +3210,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -3131,15 +3235,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -3156,15 +3260,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -3175,25 +3279,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -3215,15 +3320,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -3240,15 +3345,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -3265,15 +3370,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -3290,15 +3395,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -3315,15 +3420,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -3340,15 +3445,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -3359,25 +3464,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -3386,23 +3492,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -3413,13 +3519,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -3435,11 +3542,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -3450,11 +3557,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -3465,13 +3572,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -3485,7 +3593,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3494,17 +3611,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3521,6 +3638,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -3574,15 +3692,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -3599,15 +3717,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -3624,15 +3742,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -3649,15 +3767,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -3668,25 +3786,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -3708,15 +3827,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -3733,15 +3852,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -3758,15 +3877,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -3783,15 +3902,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -3808,15 +3927,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -3833,15 +3952,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -3852,25 +3971,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -3879,23 +3999,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -3906,13 +4026,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -3928,11 +4049,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -3943,11 +4064,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -3958,13 +4079,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -3978,7 +4100,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3987,17 +4118,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4014,6 +4145,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4067,15 +4199,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -4092,15 +4224,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -4117,15 +4249,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -4142,15 +4274,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -4161,25 +4293,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -4201,15 +4334,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -4226,15 +4359,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -4251,15 +4384,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -4276,15 +4409,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -4301,15 +4434,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -4326,15 +4459,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -4345,25 +4478,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -4372,23 +4506,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -4399,13 +4533,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -4421,11 +4556,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -4436,11 +4571,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -4451,13 +4586,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -4471,7 +4607,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4480,17 +4625,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4507,6 +4652,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4560,15 +4706,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -4585,15 +4731,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -4610,15 +4756,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -4635,15 +4781,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -4654,25 +4800,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -4694,15 +4841,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -4719,15 +4866,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -4744,15 +4891,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -4769,15 +4916,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -4794,15 +4941,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -4819,15 +4966,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -4838,25 +4985,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -4865,23 +5013,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -4892,13 +5040,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -4914,11 +5063,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -4929,11 +5078,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -4944,13 +5093,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -4964,7 +5114,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -4973,17 +5132,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5000,6 +5159,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -5053,15 +5213,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -5078,15 +5238,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -5103,15 +5263,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -5128,15 +5288,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -5147,25 +5307,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -5187,15 +5348,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -5212,15 +5373,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -5237,15 +5398,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -5262,15 +5423,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -5287,15 +5448,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -5312,15 +5473,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -5331,25 +5492,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -5358,23 +5520,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -5385,13 +5547,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -5407,11 +5570,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -5422,11 +5585,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -5437,13 +5600,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -5457,7 +5621,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -5466,17 +5639,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5493,6 +5666,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -5546,15 +5720,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -5571,15 +5745,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -5596,15 +5770,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -5621,15 +5795,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -5640,25 +5814,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -5680,15 +5855,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -5705,15 +5880,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -5730,15 +5905,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -5755,15 +5930,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -5780,15 +5955,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -5805,15 +5980,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -5824,25 +5999,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -5851,23 +6027,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -5878,13 +6054,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -5900,11 +6077,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -5915,11 +6092,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -5930,13 +6107,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -5950,7 +6128,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -5959,17 +6146,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5986,6 +6173,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -6039,15 +6227,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -6064,15 +6252,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -6089,15 +6277,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -6114,15 +6302,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -6133,25 +6321,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -6173,15 +6362,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -6198,15 +6387,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -6223,15 +6412,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -6248,15 +6437,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -6273,15 +6462,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -6298,15 +6487,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -6317,25 +6506,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -6344,23 +6534,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -6371,13 +6561,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -6393,11 +6584,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -6408,11 +6599,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -6423,13 +6614,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -6443,7 +6635,16 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -6452,17 +6653,17 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="28"/>
-    <col customWidth="1" max="2" min="2" width="16"/>
-    <col customWidth="1" max="3" min="3" width="16"/>
-    <col customWidth="1" max="4" min="4" width="16"/>
-    <col customWidth="1" max="5" min="5" width="14"/>
-    <col customWidth="1" max="6" min="6" width="14"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6479,6 +6680,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -6532,15 +6734,15 @@
       </c>
       <c r="D6" s="10">
         <f>C6-B6</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E6" s="11">
         <f>IF(B6=0,0,(C6-B6)/B6)</f>
-        <v/>
-      </c>
-      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12" t="str">
         <f>IF(ABS(E6)&lt;0.05,"✅ OK",IF(ABS(E6)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="7">
@@ -6557,15 +6759,15 @@
       </c>
       <c r="D7" s="10">
         <f>C7-B7</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E7" s="11">
         <f>IF(B7=0,0,(C7-B7)/B7)</f>
-        <v/>
-      </c>
-      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12" t="str">
         <f>IF(ABS(E7)&lt;0.05,"✅ OK",IF(ABS(E7)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="8">
@@ -6582,15 +6784,15 @@
       </c>
       <c r="D8" s="10">
         <f>C8-B8</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E8" s="11">
         <f>IF(B8=0,0,(C8-B8)/B8)</f>
-        <v/>
-      </c>
-      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12" t="str">
         <f>IF(ABS(E8)&lt;0.05,"✅ OK",IF(ABS(E8)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="9">
@@ -6607,15 +6809,15 @@
       </c>
       <c r="D9" s="10">
         <f>C9-B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E9" s="11">
         <f>IF(B9=0,0,(C9-B9)/B9)</f>
-        <v/>
-      </c>
-      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12" t="str">
         <f>IF(ABS(E9)&lt;0.05,"✅ OK",IF(ABS(E9)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="10">
@@ -6626,25 +6828,26 @@
       </c>
       <c r="B10" s="14">
         <f>B6+B7+B8+B9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C10" s="14">
         <f>C6+C7+C8+C9</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D10" s="10">
         <f>C10-B10</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E10" s="11">
         <f>IF(B10=0,0,(C10-B10)/B10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12" t="str">
         <f>IF(ABS(E10)&lt;0.05,"✅ OK",IF(ABS(E10)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -6666,15 +6869,15 @@
       </c>
       <c r="D13" s="10">
         <f>C13-B13</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E13" s="11">
         <f>IF(B13=0,0,(C13-B13)/B13)</f>
-        <v/>
-      </c>
-      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12" t="str">
         <f>IF(ABS(E13)&lt;0.05,"✅ OK",IF(ABS(E13)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="14">
@@ -6691,15 +6894,15 @@
       </c>
       <c r="D14" s="10">
         <f>C14-B14</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E14" s="11">
         <f>IF(B14=0,0,(C14-B14)/B14)</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12" t="str">
         <f>IF(ABS(E14)&lt;0.05,"✅ OK",IF(ABS(E14)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="15">
@@ -6716,15 +6919,15 @@
       </c>
       <c r="D15" s="10">
         <f>C15-B15</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E15" s="11">
         <f>IF(B15=0,0,(C15-B15)/B15)</f>
-        <v/>
-      </c>
-      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12" t="str">
         <f>IF(ABS(E15)&lt;0.05,"✅ OK",IF(ABS(E15)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="16">
@@ -6741,15 +6944,15 @@
       </c>
       <c r="D16" s="10">
         <f>C16-B16</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E16" s="11">
         <f>IF(B16=0,0,(C16-B16)/B16)</f>
-        <v/>
-      </c>
-      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12" t="str">
         <f>IF(ABS(E16)&lt;0.05,"✅ OK",IF(ABS(E16)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="17">
@@ -6766,15 +6969,15 @@
       </c>
       <c r="D17" s="10">
         <f>C17-B17</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E17" s="11">
         <f>IF(B17=0,0,(C17-B17)/B17)</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12" t="str">
         <f>IF(ABS(E17)&lt;0.05,"✅ OK",IF(ABS(E17)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="18">
@@ -6791,15 +6994,15 @@
       </c>
       <c r="D18" s="10">
         <f>C18-B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E18" s="11">
         <f>IF(B18=0,0,(C18-B18)/B18)</f>
-        <v/>
-      </c>
-      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12" t="str">
         <f>IF(ABS(E18)&lt;0.05,"✅ OK",IF(ABS(E18)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="19">
@@ -6810,25 +7013,26 @@
       </c>
       <c r="B19" s="14">
         <f>B13+B14+B15+B16+B17+B18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C19" s="14">
         <f>C13+C14+C15+C16+C17+C18</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D19" s="10">
         <f>C19-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E19" s="11">
         <f>IF(B19=0,0,(C19-B19)/B19)</f>
-        <v/>
-      </c>
-      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12" t="str">
         <f>IF(ABS(E19)&lt;0.05,"✅ OK",IF(ABS(E19)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
-      </c>
-    </row>
+        <v>✅ OK</v>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -6837,23 +7041,23 @@
       </c>
       <c r="B21" s="15">
         <f>B10-B19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C21" s="15">
         <f>C10-C19</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="D21" s="10">
         <f>C21-B21</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="11">
         <f>IF(B21=0,0,(C21-B21)/B21)</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F21" s="12" t="str">
         <f>IF(ABS(E21)&lt;0.05,"✅ OK",IF(ABS(E21)&lt;0.1,"⚠️ Atención","🔴 Alerta"))</f>
-        <v/>
+        <v>✅ OK</v>
       </c>
     </row>
     <row r="22">
@@ -6864,13 +7068,14 @@
       </c>
       <c r="B22" s="16">
         <f>IF(B10=0,0,B21/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C22" s="16">
         <f>IF(C10=0,0,C21/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
@@ -6886,11 +7091,11 @@
       </c>
       <c r="B25" s="16">
         <f>IF(B10=0,0,B13/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C25" s="16">
         <f>IF(C10=0,0,C13/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="26">
@@ -6901,11 +7106,11 @@
       </c>
       <c r="B26" s="16">
         <f>IF(B10=0,0,B14/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C26" s="16">
         <f>IF(C10=0,0,C14/C10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -6916,13 +7121,14 @@
       </c>
       <c r="B27" s="16">
         <f>IF(B10=0,0,(B13+B14)/B10)</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="C27" s="16">
         <f>IF(C10=0,0,(C13+C14)/C10)</f>
-        <v/>
-      </c>
-    </row>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="17" t="inlineStr">
         <is>
@@ -6936,6 +7142,15 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A29:F29"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>